--- a/data/chinese/P3T1_Chapter2.xlsx
+++ b/data/chinese/P3T1_Chapter2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/homes/ximonlam/Mac/單詞複習網素材/Chinese/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7F2556B-7380-9B41-BAF1-C59967FFD633}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{923C9419-6B2A-384C-8454-724E9FF61183}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="必懂寫" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
   <si>
     <t>生字</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -77,6 +77,30 @@
 3. 最後一句點明：花和蝴蝶樣子都很美麗，它們就像同一樣美好的事物，花像蝴蝶，蝴蝶也像花。
 【簡單中心思想】：詩人運用奇妙的想像，描寫花和蝴蝶一樣美麗，讚嘆大自然的美。
 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>飛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蝴蝶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在空中移動、飄行。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小鳥展翅飛向藍天。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一種昆蟲，有兩對美麗的翅膀，會在花旁飛來飛去，喜歡採花蜜。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蝴蝶在花叢中跳舞。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -504,25 +528,33 @@
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="27">
-      <c r="A2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="7">
+      <c r="A2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="3">
         <v>1</v>
       </c>
       <c r="E2" s="5"/>
     </row>
     <row r="3" spans="1:11" ht="27">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
+      <c r="A3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
       <c r="E3" s="5"/>
     </row>
     <row r="4" spans="1:11" ht="27">
